--- a/data/Reward.xlsx
+++ b/data/Reward.xlsx
@@ -428,37 +428,9 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>repeated { uint32 item; uint32 count }</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bit_index</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
